--- a/Team_Metrics_Sheet.xlsx
+++ b/Team_Metrics_Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/siddharthsharma/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TradingApp\db2026-reconX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98C9B704-4544-4B4E-9255-ACD2EF28213A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DEC797-2955-4C12-B845-0BBCEA3A9199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40540" yWindow="3380" windowWidth="29560" windowHeight="18220" tabRatio="500" firstSheet="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team 1" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="53">
   <si>
     <t>CaseStudy  - Team Assessment Rubric</t>
   </si>
@@ -59,15 +59,9 @@
     <t>Team Name:</t>
   </si>
   <si>
-    <t>Group 1</t>
-  </si>
-  <si>
     <t>Team Members (Names):</t>
   </si>
   <si>
-    <t>Abhinaya, Ananya Atri, Bindhu, Prajna, Varshita</t>
-  </si>
-  <si>
     <t>Evaluator Name:</t>
   </si>
   <si>
@@ -176,25 +170,40 @@
     <t>ReconX Project - Team Assessment Rubric</t>
   </si>
   <si>
-    <t>Group 2</t>
-  </si>
-  <si>
-    <t>Avani, Shubhang, Nandini, Vigna, Gaurav</t>
-  </si>
-  <si>
-    <t>Group 3</t>
-  </si>
-  <si>
-    <t>Rohith, Bhavesh, Payal, Pooja, Bhoomika</t>
-  </si>
-  <si>
-    <t>Group 4</t>
-  </si>
-  <si>
-    <t>Adil, Ayush Borhade, Ayush Sahu, Tushif, Radhika, Vaibhav</t>
-  </si>
-  <si>
-    <t>Group 5</t>
+    <t>David Leonard-Florin</t>
+  </si>
+  <si>
+    <t>04.08.2026</t>
+  </si>
+  <si>
+    <t>Warrior</t>
+  </si>
+  <si>
+    <t>Andrei, Toma, Ioana, Raluca, Omare, Nitika</t>
+  </si>
+  <si>
+    <t>Champ</t>
+  </si>
+  <si>
+    <t>Tiger</t>
+  </si>
+  <si>
+    <t>Jokli, Janluka, Lavinia, Alexandra, Shriya, Florin</t>
+  </si>
+  <si>
+    <t>Andrei, Shaan, Carl, Igor, Rares, Shirshajit, Tudor</t>
+  </si>
+  <si>
+    <t>Sean, Stefan, Mircea, Ana, Elif, Tejas</t>
+  </si>
+  <si>
+    <t>Rockon</t>
+  </si>
+  <si>
+    <t>Unstoppable</t>
+  </si>
+  <si>
+    <t>Metehan, Jo, Safa, Wink, Rafik, Teofil</t>
   </si>
 </sst>
 </file>
@@ -204,7 +213,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,8 +402,16 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -402,20 +419,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,319 +690,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="17"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="6">
+        <v>5</v>
+      </c>
       <c r="C14" s="7">
         <v>15</v>
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="6">
+        <v>5</v>
+      </c>
       <c r="C15" s="7">
         <v>15</v>
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="6">
+        <v>4</v>
+      </c>
       <c r="C16" s="7">
         <v>15</v>
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <v>4</v>
+      </c>
       <c r="C17" s="7">
         <v>15</v>
       </c>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="6">
+        <v>5</v>
+      </c>
       <c r="C18" s="7">
         <v>10</v>
       </c>
       <c r="D18" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6">
+        <v>5</v>
+      </c>
+      <c r="C22" s="9">
+        <v>12</v>
+      </c>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="6">
+        <v>4</v>
+      </c>
+      <c r="C23" s="9">
+        <v>12</v>
+      </c>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="9">
-        <v>12</v>
-      </c>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="6">
+        <v>5</v>
+      </c>
+      <c r="C24" s="9">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="9">
-        <v>12</v>
-      </c>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="9">
-        <v>12</v>
-      </c>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="6"/>
+      <c r="B25" s="6">
+        <v>4</v>
+      </c>
       <c r="C25" s="9">
         <v>8</v>
       </c>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="27.75" customHeight="1">
+    <row r="26" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="6">
+        <v>5</v>
+      </c>
       <c r="C26" s="9">
         <v>8</v>
       </c>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6">
+        <v>4</v>
+      </c>
+      <c r="C27" s="9">
+        <v>10</v>
+      </c>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6">
+        <v>5</v>
+      </c>
+      <c r="C28" s="9">
+        <v>10</v>
+      </c>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="9">
-        <v>10</v>
-      </c>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="6">
+        <v>5</v>
+      </c>
+      <c r="C29" s="9">
+        <v>10</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="9">
-        <v>10</v>
-      </c>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="9">
-        <v>10</v>
-      </c>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="6"/>
+      <c r="B30" s="6">
+        <v>5</v>
+      </c>
       <c r="C30" s="9">
         <v>8</v>
       </c>
       <c r="D30" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D33" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="27.75" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6">
+        <v>5</v>
+      </c>
+      <c r="C34" s="9">
+        <v>12</v>
+      </c>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6">
+        <v>5</v>
+      </c>
+      <c r="C35" s="9">
+        <v>10</v>
+      </c>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="6">
-        <v>5</v>
-      </c>
-      <c r="C34" s="9">
-        <v>12</v>
-      </c>
-      <c r="D34" s="8"/>
-    </row>
-    <row r="35" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A35" s="5" t="s">
+      <c r="B36" s="6">
+        <v>4</v>
+      </c>
+      <c r="C36" s="9">
+        <v>10</v>
+      </c>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="B35" s="6">
-        <v>5</v>
-      </c>
-      <c r="C35" s="9">
-        <v>10</v>
-      </c>
-      <c r="D35" s="8"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1">
-      <c r="A36" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="6">
-        <v>5</v>
-      </c>
-      <c r="C36" s="9">
-        <v>10</v>
-      </c>
-      <c r="D36" s="8"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="B37" s="6">
         <v>5</v>
@@ -1003,81 +1044,88 @@
       </c>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="6">
+        <v>5</v>
+      </c>
       <c r="C38" s="9">
         <v>10</v>
       </c>
       <c r="D38" s="8"/>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="18">
+        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
+        <v>4.625</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="20">
-        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
-        <v>5</v>
-      </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1">
-      <c r="A42" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="21" t="str">
+      <c r="B42" s="14" t="str">
         <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
         <v>A</v>
       </c>
-      <c r="C42" s="21"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1">
-      <c r="A44" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-    </row>
-    <row r="45" spans="1:4" ht="79.5" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A45:D48"/>
@@ -1085,11 +1133,6 @@
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1099,392 +1142,434 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81227813-7237-644B-B5F1-81070403F90E}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="17"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="6">
+        <v>5</v>
+      </c>
       <c r="C14" s="7">
         <v>15</v>
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="6">
+        <v>5</v>
+      </c>
       <c r="C15" s="7">
         <v>15</v>
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="6">
+        <v>4</v>
+      </c>
       <c r="C16" s="7">
         <v>15</v>
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <v>4</v>
+      </c>
       <c r="C17" s="7">
         <v>15</v>
       </c>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="6">
+        <v>5</v>
+      </c>
       <c r="C18" s="7">
         <v>10</v>
       </c>
       <c r="D18" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6">
+        <v>5</v>
+      </c>
+      <c r="C22" s="9">
+        <v>12</v>
+      </c>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="6">
+        <v>5</v>
+      </c>
+      <c r="C23" s="9">
+        <v>12</v>
+      </c>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="9">
-        <v>12</v>
-      </c>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="6">
+        <v>4</v>
+      </c>
+      <c r="C24" s="9">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="9">
-        <v>12</v>
-      </c>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="9">
-        <v>12</v>
-      </c>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="6"/>
+      <c r="B25" s="6">
+        <v>4</v>
+      </c>
       <c r="C25" s="9">
         <v>8</v>
       </c>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="27.75" customHeight="1">
+    <row r="26" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="6">
+        <v>5</v>
+      </c>
       <c r="C26" s="9">
         <v>8</v>
       </c>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6">
+        <v>5</v>
+      </c>
+      <c r="C27" s="9">
+        <v>10</v>
+      </c>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6">
+        <v>4</v>
+      </c>
+      <c r="C28" s="9">
+        <v>10</v>
+      </c>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="9">
-        <v>10</v>
-      </c>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="6">
+        <v>5</v>
+      </c>
+      <c r="C29" s="9">
+        <v>10</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="9">
-        <v>10</v>
-      </c>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="9">
-        <v>10</v>
-      </c>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="6"/>
+      <c r="B30" s="6">
+        <v>5</v>
+      </c>
       <c r="C30" s="9">
         <v>8</v>
       </c>
       <c r="D30" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D33" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="27.75" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6">
+        <v>5</v>
+      </c>
+      <c r="C34" s="9">
+        <v>12</v>
+      </c>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6">
+        <v>5</v>
+      </c>
+      <c r="C35" s="9">
+        <v>10</v>
+      </c>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="9">
-        <v>12</v>
-      </c>
-      <c r="D34" s="8"/>
-    </row>
-    <row r="35" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A35" s="5" t="s">
+      <c r="B36" s="6">
+        <v>4</v>
+      </c>
+      <c r="C36" s="9">
+        <v>10</v>
+      </c>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="9">
-        <v>10</v>
-      </c>
-      <c r="D35" s="8"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1">
-      <c r="A36" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="9">
-        <v>10</v>
-      </c>
-      <c r="D36" s="8"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="6"/>
+      <c r="B37" s="6">
+        <v>5</v>
+      </c>
       <c r="C37" s="9">
         <v>8</v>
       </c>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="6">
+        <v>5</v>
+      </c>
       <c r="C38" s="9">
         <v>10</v>
       </c>
       <c r="D38" s="8"/>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="18">
+        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
+        <v>4.625</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="11" t="s">
+      <c r="B42" s="14" t="str">
+        <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
+        <v>A</v>
+      </c>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1">
-      <c r="A42" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="21" t="str">
-        <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
-        <v/>
-      </c>
-      <c r="C42" s="21"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1">
-      <c r="A44" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-    </row>
-    <row r="45" spans="1:4" ht="79.5" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1508,392 +1593,434 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EAA8ADB-3F23-0E40-B965-2EE9274DF8DC}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="17"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="6">
+        <v>5</v>
+      </c>
       <c r="C14" s="7">
         <v>15</v>
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="6">
+        <v>5</v>
+      </c>
       <c r="C15" s="7">
         <v>15</v>
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="6">
+        <v>5</v>
+      </c>
       <c r="C16" s="7">
         <v>15</v>
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <v>4</v>
+      </c>
       <c r="C17" s="7">
         <v>15</v>
       </c>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="6">
+        <v>4</v>
+      </c>
       <c r="C18" s="7">
         <v>10</v>
       </c>
       <c r="D18" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6">
+        <v>4</v>
+      </c>
+      <c r="C22" s="9">
+        <v>12</v>
+      </c>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="6">
+        <v>4</v>
+      </c>
+      <c r="C23" s="9">
+        <v>12</v>
+      </c>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="9">
-        <v>12</v>
-      </c>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="6">
+        <v>4</v>
+      </c>
+      <c r="C24" s="9">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="9">
-        <v>12</v>
-      </c>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="9">
-        <v>12</v>
-      </c>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="6"/>
+      <c r="B25" s="6">
+        <v>5</v>
+      </c>
       <c r="C25" s="9">
         <v>8</v>
       </c>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="27.75" customHeight="1">
+    <row r="26" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="6">
+        <v>3</v>
+      </c>
       <c r="C26" s="9">
         <v>8</v>
       </c>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6">
+        <v>4</v>
+      </c>
+      <c r="C27" s="9">
+        <v>10</v>
+      </c>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6">
+        <v>4</v>
+      </c>
+      <c r="C28" s="9">
+        <v>10</v>
+      </c>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="9">
-        <v>10</v>
-      </c>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="6">
+        <v>5</v>
+      </c>
+      <c r="C29" s="9">
+        <v>10</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="9">
-        <v>10</v>
-      </c>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="9">
-        <v>10</v>
-      </c>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="6"/>
+      <c r="B30" s="6">
+        <v>5</v>
+      </c>
       <c r="C30" s="9">
         <v>8</v>
       </c>
       <c r="D30" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D33" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="27.75" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6">
+        <v>4</v>
+      </c>
+      <c r="C34" s="9">
+        <v>12</v>
+      </c>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6">
+        <v>4</v>
+      </c>
+      <c r="C35" s="9">
+        <v>10</v>
+      </c>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="9">
-        <v>12</v>
-      </c>
-      <c r="D34" s="8"/>
-    </row>
-    <row r="35" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A35" s="5" t="s">
+      <c r="B36" s="6">
+        <v>3</v>
+      </c>
+      <c r="C36" s="9">
+        <v>10</v>
+      </c>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="9">
-        <v>10</v>
-      </c>
-      <c r="D35" s="8"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1">
-      <c r="A36" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="9">
-        <v>10</v>
-      </c>
-      <c r="D36" s="8"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="6"/>
+      <c r="B37" s="6">
+        <v>4</v>
+      </c>
       <c r="C37" s="9">
         <v>8</v>
       </c>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="6">
+        <v>5</v>
+      </c>
       <c r="C38" s="9">
         <v>10</v>
       </c>
       <c r="D38" s="8"/>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="18">
+        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
+        <v>4.1875</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="11" t="s">
+      <c r="B42" s="14" t="str">
+        <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
+        <v>B+</v>
+      </c>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1">
-      <c r="A42" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="21" t="str">
-        <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
-        <v/>
-      </c>
-      <c r="C42" s="21"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1">
-      <c r="A44" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-    </row>
-    <row r="45" spans="1:4" ht="79.5" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1917,392 +2044,434 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEFDB7A-0BF3-9041-B68D-D372A02231CC}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="17"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1">
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="6">
+        <v>5</v>
+      </c>
       <c r="C14" s="7">
         <v>15</v>
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="6">
+        <v>5</v>
+      </c>
       <c r="C15" s="7">
         <v>15</v>
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="6">
+        <v>5</v>
+      </c>
       <c r="C16" s="7">
         <v>15</v>
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <v>5</v>
+      </c>
       <c r="C17" s="7">
         <v>15</v>
       </c>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="6">
+        <v>5</v>
+      </c>
       <c r="C18" s="7">
         <v>10</v>
       </c>
       <c r="D18" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6">
+        <v>5</v>
+      </c>
+      <c r="C22" s="9">
+        <v>12</v>
+      </c>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="6">
+        <v>5</v>
+      </c>
+      <c r="C23" s="9">
+        <v>12</v>
+      </c>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="9">
-        <v>12</v>
-      </c>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="6">
+        <v>5</v>
+      </c>
+      <c r="C24" s="9">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="9">
-        <v>12</v>
-      </c>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="9">
-        <v>12</v>
-      </c>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="6"/>
+      <c r="B25" s="6">
+        <v>5</v>
+      </c>
       <c r="C25" s="9">
         <v>8</v>
       </c>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="27.75" customHeight="1">
+    <row r="26" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="6">
+        <v>5</v>
+      </c>
       <c r="C26" s="9">
         <v>8</v>
       </c>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6">
+        <v>5</v>
+      </c>
+      <c r="C27" s="9">
+        <v>10</v>
+      </c>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6">
+        <v>5</v>
+      </c>
+      <c r="C28" s="9">
+        <v>10</v>
+      </c>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="9">
-        <v>10</v>
-      </c>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="6">
+        <v>5</v>
+      </c>
+      <c r="C29" s="9">
+        <v>10</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="9">
-        <v>10</v>
-      </c>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="9">
-        <v>10</v>
-      </c>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="6"/>
+      <c r="B30" s="6">
+        <v>5</v>
+      </c>
       <c r="C30" s="9">
         <v>8</v>
       </c>
       <c r="D30" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D33" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="27.75" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6">
+        <v>5</v>
+      </c>
+      <c r="C34" s="9">
+        <v>12</v>
+      </c>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6">
+        <v>5</v>
+      </c>
+      <c r="C35" s="9">
+        <v>10</v>
+      </c>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="9">
-        <v>12</v>
-      </c>
-      <c r="D34" s="8"/>
-    </row>
-    <row r="35" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A35" s="5" t="s">
+      <c r="B36" s="6">
+        <v>5</v>
+      </c>
+      <c r="C36" s="9">
+        <v>10</v>
+      </c>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="9">
-        <v>10</v>
-      </c>
-      <c r="D35" s="8"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1">
-      <c r="A36" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="9">
-        <v>10</v>
-      </c>
-      <c r="D36" s="8"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="6"/>
+      <c r="B37" s="6">
+        <v>5</v>
+      </c>
       <c r="C37" s="9">
         <v>8</v>
       </c>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="6">
+        <v>5</v>
+      </c>
       <c r="C38" s="9">
         <v>10</v>
       </c>
       <c r="D38" s="8"/>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="18">
+        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
+        <v>5</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="11" t="s">
+      <c r="B42" s="14" t="str">
+        <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
+        <v>A</v>
+      </c>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1">
-      <c r="A42" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="21" t="str">
-        <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
-        <v/>
-      </c>
-      <c r="C42" s="21"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1">
-      <c r="A44" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-    </row>
-    <row r="45" spans="1:4" ht="79.5" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2326,390 +2495,434 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB2C291-B5C3-DF42-87C1-E157CBDFA90F}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="17"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="6">
+        <v>5</v>
+      </c>
       <c r="C14" s="7">
         <v>15</v>
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="6">
+        <v>5</v>
+      </c>
       <c r="C15" s="7">
         <v>15</v>
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="6">
+        <v>4</v>
+      </c>
       <c r="C16" s="7">
         <v>15</v>
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <v>5</v>
+      </c>
       <c r="C17" s="7">
         <v>15</v>
       </c>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="6">
+        <v>5</v>
+      </c>
       <c r="C18" s="7">
         <v>10</v>
       </c>
       <c r="D18" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6">
+        <v>4</v>
+      </c>
+      <c r="C22" s="9">
+        <v>12</v>
+      </c>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="6">
+        <v>4</v>
+      </c>
+      <c r="C23" s="9">
+        <v>12</v>
+      </c>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="9">
-        <v>12</v>
-      </c>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="6">
+        <v>5</v>
+      </c>
+      <c r="C24" s="9">
+        <v>12</v>
+      </c>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="9">
-        <v>12</v>
-      </c>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="9">
-        <v>12</v>
-      </c>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="6"/>
+      <c r="B25" s="6">
+        <v>4</v>
+      </c>
       <c r="C25" s="9">
         <v>8</v>
       </c>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="27.75" customHeight="1">
+    <row r="26" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="B26" s="6">
+        <v>5</v>
+      </c>
       <c r="C26" s="9">
         <v>8</v>
       </c>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6">
+        <v>4</v>
+      </c>
+      <c r="C27" s="9">
+        <v>10</v>
+      </c>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6">
+        <v>5</v>
+      </c>
+      <c r="C28" s="9">
+        <v>10</v>
+      </c>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="9">
-        <v>10</v>
-      </c>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="B29" s="6">
+        <v>4</v>
+      </c>
+      <c r="C29" s="9">
+        <v>10</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="9">
-        <v>10</v>
-      </c>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="9">
-        <v>10</v>
-      </c>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="6"/>
+      <c r="B30" s="6">
+        <v>5</v>
+      </c>
       <c r="C30" s="9">
         <v>8</v>
       </c>
       <c r="D30" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D33" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="27.75" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6">
+        <v>5</v>
+      </c>
+      <c r="C34" s="9">
+        <v>12</v>
+      </c>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6">
+        <v>5</v>
+      </c>
+      <c r="C35" s="9">
+        <v>10</v>
+      </c>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="9">
-        <v>12</v>
-      </c>
-      <c r="D34" s="8"/>
-    </row>
-    <row r="35" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A35" s="5" t="s">
+      <c r="B36" s="6">
+        <v>5</v>
+      </c>
+      <c r="C36" s="9">
+        <v>10</v>
+      </c>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="9">
-        <v>10</v>
-      </c>
-      <c r="D35" s="8"/>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1">
-      <c r="A36" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="9">
-        <v>10</v>
-      </c>
-      <c r="D36" s="8"/>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="6"/>
+      <c r="B37" s="6">
+        <v>5</v>
+      </c>
       <c r="C37" s="9">
         <v>8</v>
       </c>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="6">
+        <v>4</v>
+      </c>
       <c r="C38" s="9">
         <v>10</v>
       </c>
       <c r="D38" s="8"/>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="18">
+        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
+        <v>4.625</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="20" t="str">
-        <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="11" t="s">
+      <c r="B42" s="14" t="str">
+        <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
+        <v>A</v>
+      </c>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1">
-      <c r="A42" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="21" t="str">
-        <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
-        <v/>
-      </c>
-      <c r="C42" s="21"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1">
-      <c r="A44" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-    </row>
-    <row r="45" spans="1:4" ht="79.5" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2733,95 +2946,95 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4EA062D-0206-E34D-B253-F8906AE9DFE2}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="17"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="7">
@@ -2829,9 +3042,9 @@
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7">
@@ -2839,9 +3052,9 @@
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="7">
@@ -2849,9 +3062,9 @@
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="7">
@@ -2859,9 +3072,9 @@
       </c>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="7">
@@ -2869,31 +3082,31 @@
       </c>
       <c r="D18" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="9">
@@ -2901,9 +3114,9 @@
       </c>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="9">
@@ -2911,9 +3124,9 @@
       </c>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="9">
@@ -2921,9 +3134,9 @@
       </c>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="9">
@@ -2931,9 +3144,9 @@
       </c>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="27.75" customHeight="1">
+    <row r="26" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="9">
@@ -2941,9 +3154,9 @@
       </c>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="9">
@@ -2951,9 +3164,9 @@
       </c>
       <c r="D27" s="8"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="9">
@@ -2961,9 +3174,9 @@
       </c>
       <c r="D28" s="8"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="9">
@@ -2971,9 +3184,9 @@
       </c>
       <c r="D29" s="8"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="9">
@@ -2981,31 +3194,31 @@
       </c>
       <c r="D30" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D33" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="27.75" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="9">
@@ -3013,9 +3226,9 @@
       </c>
       <c r="D34" s="8"/>
     </row>
-    <row r="35" spans="1:4" ht="27.75" customHeight="1">
+    <row r="35" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="9">
@@ -3023,9 +3236,9 @@
       </c>
       <c r="D35" s="8"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="9">
@@ -3033,9 +3246,9 @@
       </c>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="9">
@@ -3043,9 +3256,9 @@
       </c>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="9">
@@ -3053,68 +3266,68 @@
       </c>
       <c r="D38" s="8"/>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="20" t="str">
+        <v>36</v>
+      </c>
+      <c r="B41" s="18" t="str">
         <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
         <v/>
       </c>
-      <c r="C41" s="20"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="21" t="str">
+        <v>38</v>
+      </c>
+      <c r="B42" s="14" t="str">
         <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
         <v/>
       </c>
-      <c r="C42" s="21"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1">
-      <c r="A44" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-    </row>
-    <row r="45" spans="1:4" ht="79.5" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3138,95 +3351,95 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1129DA87-3363-AF46-B00E-03AC911FD482}">
   <dimension ref="A1:D48"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="35" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="17"/>
     </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1">
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1">
-      <c r="A12" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
     </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1">
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="7">
@@ -3234,9 +3447,9 @@
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1">
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7">
@@ -3244,9 +3457,9 @@
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1">
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="7">
@@ -3254,9 +3467,9 @@
       </c>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="7">
@@ -3264,9 +3477,9 @@
       </c>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="7">
@@ -3274,31 +3487,31 @@
       </c>
       <c r="D18" s="8"/>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
     </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="9">
@@ -3306,9 +3519,9 @@
       </c>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="9">
@@ -3316,9 +3529,9 @@
       </c>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1">
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="9">
@@ -3326,9 +3539,9 @@
       </c>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1">
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="9">
@@ -3336,9 +3549,9 @@
       </c>
       <c r="D25" s="8"/>
     </row>
-    <row r="26" spans="1:4" ht="27.75" customHeight="1">
+    <row r="26" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="9">
@@ -3346,9 +3559,9 @@
       </c>
       <c r="D26" s="8"/>
     </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1">
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="9">
@@ -3356,9 +3569,9 @@
       </c>
       <c r="D27" s="8"/>
     </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1">
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="9">
@@ -3366,9 +3579,9 @@
       </c>
       <c r="D28" s="8"/>
     </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1">
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="9">
@@ -3376,9 +3589,9 @@
       </c>
       <c r="D29" s="8"/>
     </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="9">
@@ -3386,31 +3599,31 @@
       </c>
       <c r="D30" s="8"/>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1">
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="D33" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="27.75" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="9">
@@ -3418,9 +3631,9 @@
       </c>
       <c r="D34" s="8"/>
     </row>
-    <row r="35" spans="1:4" ht="27.75" customHeight="1">
+    <row r="35" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="9">
@@ -3428,9 +3641,9 @@
       </c>
       <c r="D35" s="8"/>
     </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="9">
@@ -3438,9 +3651,9 @@
       </c>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1">
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="9">
@@ -3448,9 +3661,9 @@
       </c>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="9">
@@ -3458,68 +3671,68 @@
       </c>
       <c r="D38" s="8"/>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1">
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="20" t="str">
+        <v>36</v>
+      </c>
+      <c r="B41" s="18" t="str">
         <f>IFERROR(AVERAGE(B14:B18,B21:B29,B32:B36),"")</f>
         <v/>
       </c>
-      <c r="C41" s="20"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="21" t="str">
+        <v>38</v>
+      </c>
+      <c r="B42" s="14" t="str">
         <f>IF(B41="","",IF(B41&gt;=4.5,"A",IF(B41&gt;=4,"B+",IF(B41&gt;=3.5,"B",IF(B41&gt;=3,"C+",IF(B41&gt;=2.5,"C","D"))))))</f>
         <v/>
       </c>
-      <c r="C42" s="21"/>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1">
-      <c r="A44" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-    </row>
-    <row r="45" spans="1:4" ht="79.5" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+    </row>
+    <row r="45" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
